--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487102_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487102_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1824</v>
+        <v>1.7356</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2434</v>
+        <v>5.6628</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.0611</v>
+        <v>-3.9272</v>
       </c>
       <c r="G2" t="n">
         <v>0.8282</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.2573</v>
+        <v>-1.704</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6657</v>
+        <v>-1.2463</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5916</v>
+        <v>-0.4578</v>
       </c>
       <c r="V2" t="n">
         <v>4.5415</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5341</v>
+        <v>0.5599</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7181</v>
+        <v>1.8778</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.184</v>
+        <v>-1.3179</v>
       </c>
       <c r="G3" t="n">
         <v>-1.828</v>
@@ -688,13 +688,13 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8309</v>
+        <v>-0.8051</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8923</v>
+        <v>-0.7327</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0614</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>1.842</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4475</v>
+        <v>0.5198</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5627</v>
+        <v>2.5815</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1152</v>
+        <v>-2.0616</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1223</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7463</v>
+        <v>-1.674</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9386</v>
+        <v>-0.9197</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8078</v>
+        <v>-0.7542</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. AREVALO NEGUERUELA</t>
+          <t>N. KIAMESO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0737</v>
+        <v>-1.8312</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6995</v>
+        <v>-0.1333</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3742</v>
+        <v>-1.6979</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2679</v>
+        <v>-0.5844</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2614</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0064</v>
+        <v>0.1742</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6055</v>
+        <v>0.1235</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6055</v>
+        <v>0.0828</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6624</v>
+        <v>-0.7079</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6559</v>
+        <v>-0.8414</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0064</v>
+        <v>0.1335</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2617</v>
+        <v>-0.2118</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3569</v>
+        <v>-0.2568</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0449</v>
       </c>
       <c r="V5" t="n">
-        <v>1.228</v>
+        <v>-1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. KIAMESO</t>
+          <t>A. AREVALO NEGUERUELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0979</v>
+        <v>-2.0201</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2929</v>
+        <v>-0.6995</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.805</v>
+        <v>-1.3206</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5844</v>
+        <v>-2.2679</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-2.2614</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1742</v>
+        <v>-0.0064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1235</v>
+        <v>-0.6055</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0828</v>
+        <v>-0.6055</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7079</v>
+        <v>-1.6624</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8414</v>
+        <v>-1.6559</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1335</v>
+        <v>-0.0064</v>
       </c>
       <c r="P6" t="n">
-        <v>0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
         <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4785</v>
+        <v>-0.2082</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4164</v>
+        <v>-0.3569</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0621</v>
+        <v>0.1487</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.228</v>
+        <v>1.228</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>D. IBARLUCEA LAVIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.1583</v>
+        <v>-6.7312</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2226</v>
+        <v>-1.3948</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.9356</v>
+        <v>-5.3364</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.4925</v>
+        <v>1.4055</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.2229</v>
+        <v>-1.1</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2695</v>
+        <v>2.5055</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6941000000000001</v>
+        <v>4.4096</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4499</v>
+        <v>1.8784</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2442</v>
+        <v>2.5312</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.1866</v>
+        <v>-3.0041</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.6729</v>
+        <v>-2.9784</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5137</v>
+        <v>-0.0257</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-4.8252</v>
       </c>
       <c r="R8" t="n">
         <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3027</v>
+        <v>-1.7929</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3304</v>
+        <v>-0.9792</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0277</v>
+        <v>-0.8137</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5561</v>
+        <v>-3.6417</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8999</v>
+        <v>-3.6417</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. IBARLUCEA LAVIN</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.8512</v>
+        <v>-7.0615</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3542</v>
+        <v>-2.8046</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.497</v>
+        <v>-4.2569</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4055</v>
+        <v>-4.4925</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1</v>
+        <v>-3.2229</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5055</v>
+        <v>-1.2695</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4096</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8784</v>
+        <v>0.4499</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5312</v>
+        <v>0.2442</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0041</v>
+        <v>-5.1866</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.9784</v>
+        <v>-3.6729</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0257</v>
+        <v>-1.5137</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7021</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.8252</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
         <v>2.1231</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9129</v>
+        <v>-1.206</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9386</v>
+        <v>-0.9125</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.2935</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.6417</v>
+        <v>-1.5561</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.6417</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.558199999999999</v>
+        <v>-9.1516</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.171</v>
+        <v>-3.711</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.3871</v>
+        <v>-5.4407</v>
       </c>
       <c r="G10" t="n">
         <v>-8.014900000000001</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9063</v>
+        <v>-1.4998</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4277</v>
+        <v>-0.9677</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4786</v>
+        <v>-0.5321</v>
       </c>
       <c r="V10" t="n">
         <v>0.9421</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-27.7646</v>
+        <v>-27.1696</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3038</v>
+        <v>-0.7089000000000012</v>
       </c>
       <c r="F11" t="n">
         <v>-26.4606</v>
@@ -1303,7 +1303,7 @@
         <v>-6.2335</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8601</v>
+        <v>-3.860099999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-15.4407</v>
@@ -1312,10 +1312,10 @@
         <v>11.5806</v>
       </c>
       <c r="S11" t="n">
-        <v>-9.8751</v>
+        <v>-9.2803</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.145099999999999</v>
+        <v>-6.550299999999999</v>
       </c>
       <c r="U11" t="n">
         <v>-2.7301</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.1778</v>
+        <v>18.0721</v>
       </c>
       <c r="E12" t="n">
-        <v>14.3836</v>
+        <v>15.385</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7941</v>
+        <v>2.6871</v>
       </c>
       <c r="G12" t="n">
         <v>12.2931</v>
@@ -1390,13 +1390,13 @@
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5988</v>
+        <v>1.4932</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6993</v>
+        <v>0.3021</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2981</v>
+        <v>1.1911</v>
       </c>
       <c r="V12" t="n">
         <v>2.7418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3262</v>
+        <v>13.6114</v>
       </c>
       <c r="E13" t="n">
-        <v>11.906</v>
+        <v>11.4053</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4202</v>
+        <v>2.206</v>
       </c>
       <c r="G13" t="n">
         <v>7.0775</v>
@@ -1468,13 +1468,13 @@
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8277</v>
+        <v>2.1128</v>
       </c>
       <c r="T13" t="n">
-        <v>1.17</v>
+        <v>0.6693</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6577</v>
+        <v>1.4436</v>
       </c>
       <c r="V13" t="n">
         <v>3.0699</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5789</v>
+        <v>3.6513</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0907</v>
+        <v>2.5914</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4881</v>
+        <v>1.0598</v>
       </c>
       <c r="G14" t="n">
         <v>1.1962</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0086</v>
+        <v>1.081</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6398</v>
+        <v>-0.1391</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6485</v>
+        <v>1.2201</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9421</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7041</v>
+        <v>1.7062</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7264</v>
+        <v>2.868</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0223</v>
+        <v>-1.1618</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6105</v>
+        <v>1.0224</v>
       </c>
       <c r="H15" t="n">
-        <v>2.281</v>
+        <v>-1.3902</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6705</v>
+        <v>2.4127</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0916</v>
+        <v>3.0114</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9288</v>
+        <v>0.4395</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1628</v>
+        <v>2.5719</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4811</v>
+        <v>-1.989</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6478</v>
+        <v>-1.8297</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8333</v>
+        <v>-0.1592</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.7021</v>
+        <v>1.5441</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>1.158</v>
+        <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0815</v>
+        <v>1.3098</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2091</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.774</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2859</v>
+        <v>-2.1701</v>
       </c>
       <c r="W15" t="n">
         <v>0.2859</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5717</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5386</v>
+        <v>0.1812</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9681</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4295</v>
+        <v>-0.3435</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0224</v>
+        <v>1.6105</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3902</v>
+        <v>2.281</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4127</v>
+        <v>-0.6705</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0114</v>
+        <v>3.0916</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4395</v>
+        <v>2.9288</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5719</v>
+        <v>0.1628</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.989</v>
+        <v>-1.4811</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8297</v>
+        <v>-0.6478</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1592</v>
+        <v>-0.8333</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5441</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5091</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1422</v>
+        <v>1.5586</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6359</v>
+        <v>1.0074</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5063</v>
+        <v>0.5512</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1701</v>
+        <v>-0.2859</v>
       </c>
       <c r="W16" t="n">
         <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4559</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5586</v>
+        <v>-0.7649</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4182</v>
+        <v>0.9175</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9768</v>
+        <v>-1.6823</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7228</v>
@@ -1780,13 +1780,13 @@
         <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8481</v>
+        <v>0.6418</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8593</v>
+        <v>0.3586</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0112</v>
+        <v>0.2832</v>
       </c>
       <c r="V17" t="n">
         <v>-1.842</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5069</v>
+        <v>-1.2462</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1118</v>
+        <v>-0.0117</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3951</v>
+        <v>-1.2345</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2482</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1309</v>
+        <v>0.1299</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2974</v>
+        <v>-0.1973</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1666</v>
+        <v>0.3272</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5138</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1919</v>
+        <v>-2.951</v>
       </c>
       <c r="E19" t="n">
         <v>-4.4335</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2416</v>
+        <v>1.4825</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6112</v>
@@ -1936,13 +1936,13 @@
         <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4422</v>
+        <v>0.6831</v>
       </c>
       <c r="T19" t="n">
         <v>0.1917</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2505</v>
+        <v>0.4914</v>
       </c>
       <c r="V19" t="n">
         <v>0.3281</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.3036</v>
+        <v>-4.4955</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.487</v>
+        <v>-2.786</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8166</v>
+        <v>-1.7095</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4606</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0568</v>
+        <v>0.8649</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6993</v>
+        <v>0.0017</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7561</v>
+        <v>0.8632</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5138</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>27.7646</v>
+        <v>27.76459999999999</v>
       </c>
       <c r="E21" t="n">
         <v>26.4607</v>
       </c>
       <c r="F21" t="n">
-        <v>1.303699999999999</v>
+        <v>1.3038</v>
       </c>
       <c r="G21" t="n">
         <v>16.1569</v>
@@ -2062,7 +2062,7 @@
         <v>10.1165</v>
       </c>
       <c r="I21" t="n">
-        <v>6.0405</v>
+        <v>6.040500000000001</v>
       </c>
       <c r="J21" t="n">
         <v>28.0701</v>
@@ -2080,7 +2080,7 @@
         <v>-11.7201</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1928</v>
+        <v>-0.1928000000000001</v>
       </c>
       <c r="P21" t="n">
         <v>3.8602</v>
@@ -2092,22 +2092,22 @@
         <v>15.4406</v>
       </c>
       <c r="S21" t="n">
-        <v>9.875</v>
+        <v>9.875100000000002</v>
       </c>
       <c r="T21" t="n">
         <v>2.7302</v>
       </c>
       <c r="U21" t="n">
-        <v>7.1451</v>
+        <v>7.145</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.127899999999999</v>
+        <v>-2.1279</v>
       </c>
       <c r="W21" t="n">
         <v>7.241199999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-9.3689</v>
+        <v>-9.368900000000002</v>
       </c>
     </row>
   </sheetData>
